--- a/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>KITT</t>
   </si>
@@ -656,97 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5200</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,35 +763,38 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4400</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -806,29 +813,32 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,29 +877,30 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,29 +1007,32 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
       </c>
       <c r="H15" s="3">
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,14 +1045,17 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,70 +1068,74 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E17" s="3">
         <v>8000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
       <c r="M17" s="3">
         <v>0</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5200</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1124,8 +1154,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,29 +1174,30 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E20" s="3">
         <v>27600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1182,29 +1216,32 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E21" s="3">
         <v>20700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-12800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6900</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1223,8 +1260,11 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,49 +1304,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E23" s="3">
         <v>20700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4400</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
         <v>0</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1322,17 +1368,17 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1340,14 +1386,17 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E26" s="3">
         <v>20700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4400</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
         <v>0</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E27" s="3">
         <v>20700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4400</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
         <v>0</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,29 +1700,32 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-27600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1674,49 +1744,55 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E33" s="3">
         <v>20700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4400</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
         <v>0</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E35" s="3">
         <v>20700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4400</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
         <v>0</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E41" s="3">
         <v>4400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>35900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="N41" s="3">
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1930,11 +2020,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1950,8 +2040,8 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1959,26 +2049,29 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1994,32 +2087,35 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E44" s="3">
         <v>12500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5600</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2035,44 +2131,47 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E45" s="3">
         <v>6400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5300</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,49 +2181,55 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E46" s="3">
         <v>25200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>48000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
+      <c r="N46" s="3">
+        <v>0</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,26 +2269,29 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E48" s="3">
         <v>23200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2199,14 +2307,17 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2246,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2445,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2340,16 +2460,16 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>174500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>174200</v>
       </c>
       <c r="J52" s="3">
         <v>174200</v>
@@ -2358,19 +2478,22 @@
         <v>174200</v>
       </c>
       <c r="L52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E54" s="3">
         <v>48500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>49500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>52600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>58000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>174700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>174600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>174800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>175600</v>
-      </c>
-      <c r="L54" s="3">
-        <v>200</v>
       </c>
       <c r="M54" s="3">
         <v>200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
+      <c r="N54" s="3">
+        <v>200</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,8 +2615,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2494,29 +2625,29 @@
         <v>5700</v>
       </c>
       <c r="E57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
       </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2526,8 +2657,11 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2537,138 +2671,147 @@
       <c r="E58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E59" s="3">
         <v>7800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>200</v>
       </c>
       <c r="L59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>600</v>
-      </c>
-      <c r="J60" s="3">
-        <v>300</v>
       </c>
       <c r="K60" s="3">
         <v>300</v>
       </c>
       <c r="L60" s="3">
+        <v>300</v>
+      </c>
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E61" s="3">
         <v>17800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2690,38 +2833,41 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E62" s="3">
         <v>6800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>34900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>32800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>32400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E66" s="3">
         <v>38200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>62300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>52600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>51800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-79200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-61600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-82200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-68100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-59900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11600</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
       <c r="M72" s="3">
         <v>0</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>0</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E76" s="3">
         <v>10300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-12800</v>
       </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
       <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
         <v>6300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>167700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>168500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>166500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>162700</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
       <c r="M76" s="3">
         <v>0</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>0</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E81" s="3">
         <v>20700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4400</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
         <v>0</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>0</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,23 +3624,24 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3458,8 +3657,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3467,8 +3666,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3950,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,8 +4080,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3862,31 +4092,31 @@
         <v>-4600</v>
       </c>
       <c r="E94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F94" s="3">
         <v>3500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12400</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -3894,8 +4124,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4318,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>52900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>KITT</t>
   </si>
@@ -656,107 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="E8" s="3">
         <v>1100</v>
       </c>
       <c r="F8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H8" s="3">
         <v>2800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5200</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -766,41 +773,47 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F9" s="3">
         <v>2700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>4400</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,35 +829,41 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F10" s="3">
         <v>-1100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -860,8 +879,14 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,35 +903,37 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>400</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>300</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
       </c>
       <c r="I12" s="3">
+        <v>300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>200</v>
+      </c>
+      <c r="K12" s="3">
         <v>1900</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,31 +999,37 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>26800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1010,35 +1049,41 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>400</v>
+      </c>
+      <c r="E15" s="3">
         <v>200</v>
       </c>
-      <c r="E15" s="3">
-        <v>100</v>
-      </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
       </c>
       <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1048,14 +1093,20 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,79 +1120,87 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>35300</v>
+      </c>
+      <c r="F17" s="3">
         <v>9800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>10400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>9000</v>
       </c>
       <c r="I17" s="3">
         <v>10400</v>
       </c>
       <c r="J17" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>10400</v>
+      </c>
+      <c r="L17" s="3">
         <v>500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-6900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-5800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-7200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5200</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1157,8 +1216,14 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,35 +1240,37 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-9500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>27600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-8300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-7100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1219,35 +1286,41 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-17500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>20700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-13900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-8100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-12800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-6900</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1263,8 +1336,14 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,52 +1386,64 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-17700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>20700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-14100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-8200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-13200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4400</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1371,32 +1462,38 @@
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1536,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-17700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>20700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-14100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-13200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4400</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-17700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>20700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-14100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-18100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4400</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,35 +1836,41 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F32" s="3">
         <v>9500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-27600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>8300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>7100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1747,52 +1886,64 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-17700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>20700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-14100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-18100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4400</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1986,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-17700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>20700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-14100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-18100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4400</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,57 +2135,65 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>800</v>
+      </c>
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>17800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>35900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2023,14 +2202,14 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>5000</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2043,41 +2222,47 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2090,38 +2275,44 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F44" s="3">
         <v>14000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>12500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>11000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2134,102 +2325,120 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
         <v>6100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
+        <v>6100</v>
+      </c>
+      <c r="G45" s="3">
         <v>6400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5300</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F46" s="3">
         <v>27900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>25200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>32100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>37000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>48000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1400</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2272,32 +2481,38 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F48" s="3">
         <v>28400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>23200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>17200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>15500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>10000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2310,14 +2525,20 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2581,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2681,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>174500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>174200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>174200</v>
       </c>
       <c r="L52" s="3">
         <v>174200</v>
       </c>
       <c r="M52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="N52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2781,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F54" s="3">
         <v>56300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>48500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>49500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>52600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>58000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>174700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>174600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>174800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>175600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,52 +2875,60 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F57" s="3">
         <v>5700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2800</v>
       </c>
       <c r="I57" s="3">
         <v>300</v>
       </c>
       <c r="J57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K57" s="3">
+        <v>300</v>
+      </c>
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2674,150 +2941,168 @@
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F59" s="3">
         <v>7200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>8000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F60" s="3">
         <v>13000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>13600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>31600</v>
+      </c>
+      <c r="F61" s="3">
         <v>29900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>17800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>16800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>15900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>15000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2836,52 +3121,64 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F62" s="3">
         <v>16100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>6800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>34900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>32800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>32400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>5600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>8000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>12700</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3321,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>67900</v>
+      </c>
+      <c r="F66" s="3">
         <v>59000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>38200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>62300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>52600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>51800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3591,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-118400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-79200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-61600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-82200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-68100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-59900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-6700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-5800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-7700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-11600</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3791,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-2700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-12800</v>
       </c>
-      <c r="G76" s="3">
-        <v>0</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
         <v>6300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>167700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>168500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>166500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>162700</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O76" s="3">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3891,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-17700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>20700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-14100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-18100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4400</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,28 +4020,30 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>100</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3660,17 +4057,23 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-8800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-30800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4390,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3995,8 +4436,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4536,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>3500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-12400</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4610,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4806,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>10500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>52900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,48 +4906,60 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-8100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-18100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>15300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-200</v>
       </c>
       <c r="K102" s="3">
         <v>-300</v>
       </c>
       <c r="L102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>KITT</t>
   </si>
@@ -656,87 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -744,29 +748,29 @@
         <v>500</v>
       </c>
       <c r="E8" s="3">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3">
         <v>1100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -779,44 +783,47 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4400</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,38 +842,41 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,38 +918,39 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1900</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,20 +1022,23 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>26800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1028,11 +1048,11 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1064,29 +1087,29 @@
         <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
       </c>
       <c r="G15" s="3">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
       </c>
       <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1099,14 +1122,17 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,88 +1148,92 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E17" s="3">
         <v>6000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
       <c r="P17" s="3">
         <v>0</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
+      <c r="Q17" s="3">
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-34200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1222,8 +1252,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,38 +1275,39 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>5900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>27600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1292,38 +1326,41 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-39300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-17500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,8 +1379,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,93 +1432,99 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
         <v>400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-39500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4400</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
+      <c r="Q23" s="3">
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1486,14 +1532,17 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
         <v>400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-39500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4400</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="Q26" s="3">
+        <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-39500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4400</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="Q27" s="3">
+        <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,38 +1909,41 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-27600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1892,58 +1962,64 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-39500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4400</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="Q33" s="3">
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-39500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4400</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
         <v>0</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="Q35" s="3">
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,66 +2223,70 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E41" s="3">
         <v>6200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
+      <c r="Q41" s="3">
+        <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2208,11 +2298,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>5000</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,8 +2318,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2237,35 +2327,38 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2281,14 +2374,17 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2299,23 +2395,23 @@
         <v>2200</v>
       </c>
       <c r="F44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G44" s="3">
         <v>14000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5600</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2331,53 +2427,56 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E45" s="3">
         <v>3300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>6100</v>
       </c>
       <c r="F45" s="3">
         <v>6100</v>
       </c>
       <c r="G45" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H45" s="3">
         <v>6400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5300</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2387,58 +2486,64 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E46" s="3">
         <v>11800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>32100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1400</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
+      <c r="Q46" s="3">
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2487,35 +2592,38 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E48" s="3">
         <v>17400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,14 +2639,17 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2699,7 +2819,7 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
@@ -2708,16 +2828,16 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>174500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>174200</v>
       </c>
       <c r="M52" s="3">
         <v>174200</v>
@@ -2726,19 +2846,22 @@
         <v>174200</v>
       </c>
       <c r="O52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E54" s="3">
         <v>29400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>56300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>52600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>58000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>174700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>174600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>174800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>175600</v>
-      </c>
-      <c r="O54" s="3">
-        <v>200</v>
       </c>
       <c r="P54" s="3">
         <v>200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
+      <c r="Q54" s="3">
+        <v>200</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,47 +3007,48 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>5700</v>
       </c>
       <c r="G57" s="3">
         <v>5700</v>
       </c>
       <c r="H57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,25 +3058,28 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2954,158 +3088,167 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E59" s="3">
         <v>7300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>200</v>
       </c>
       <c r="O59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E60" s="3">
         <v>14000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
-      </c>
-      <c r="M60" s="3">
-        <v>300</v>
       </c>
       <c r="N60" s="3">
         <v>300</v>
       </c>
       <c r="O60" s="3">
+        <v>300</v>
+      </c>
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E61" s="3">
         <v>44900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>31600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3127,47 +3270,50 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
         <v>10000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>34900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12700</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E66" s="3">
         <v>68900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>67900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>59000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>62300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-123800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-118400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-118800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-79200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-61600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-82200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-68100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-59900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11600</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
       <c r="P72" s="3">
         <v>0</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
+      <c r="Q72" s="3">
+        <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-39500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-41800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-12800</v>
       </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
       <c r="J76" s="3">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3">
         <v>6300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>167700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>168500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>166500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>162700</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
       <c r="P76" s="3">
         <v>0</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-39500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4400</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
         <v>0</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="Q81" s="3">
+        <v>0</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4031,23 +4230,23 @@
         <v>400</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
+        <v>200</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4063,8 +4262,8 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,49 +4769,52 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-4600</v>
       </c>
       <c r="G94" s="3">
         <v>-4600</v>
       </c>
       <c r="H94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I94" s="3">
         <v>3500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12400</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -4592,8 +4822,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E100" s="3">
         <v>12000</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>10500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>52900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>KITT</t>
   </si>
@@ -656,124 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3">
         <v>500</v>
       </c>
       <c r="F8" s="3">
+        <v>500</v>
+      </c>
+      <c r="G8" s="3">
         <v>1100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -786,47 +790,50 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E9" s="3">
         <v>2900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4400</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -845,41 +852,44 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1600</v>
       </c>
-      <c r="F10" s="3">
-        <v>-3300</v>
-      </c>
       <c r="G10" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="H10" s="3">
         <v>-1100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -898,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,41 +932,42 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,22 +1042,25 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>26800</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>25500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1048,14 +1068,14 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1078,8 +1098,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1090,29 +1113,29 @@
         <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
       </c>
       <c r="L15" s="3">
+        <v>100</v>
+      </c>
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1125,14 +1148,17 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,94 +1175,98 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E17" s="3">
         <v>6500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
-        <v>35300</v>
-      </c>
       <c r="G17" s="3">
+        <v>13900</v>
+      </c>
+      <c r="H17" s="3">
         <v>9800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5500</v>
       </c>
-      <c r="F18" s="3">
-        <v>-34200</v>
-      </c>
       <c r="G18" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="H18" s="3">
         <v>-8200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1255,8 +1285,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,41 +1309,42 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>600</v>
+        <v>1700</v>
       </c>
       <c r="E20" s="3">
-        <v>5900</v>
+        <v>-4300</v>
       </c>
       <c r="F20" s="3">
-        <v>-5400</v>
+        <v>-8400</v>
       </c>
       <c r="G20" s="3">
-        <v>-9500</v>
+        <v>3500</v>
       </c>
       <c r="H20" s="3">
-        <v>27600</v>
+        <v>8600</v>
       </c>
       <c r="I20" s="3">
-        <v>-8300</v>
+        <v>-29100</v>
       </c>
       <c r="J20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1600</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1329,41 +1363,44 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5000</v>
+        <v>-6800</v>
       </c>
       <c r="E21" s="3">
-        <v>800</v>
+        <v>-1300</v>
       </c>
       <c r="F21" s="3">
-        <v>-39300</v>
+        <v>3300</v>
       </c>
       <c r="G21" s="3">
-        <v>-17500</v>
+        <v>-16100</v>
       </c>
       <c r="H21" s="3">
-        <v>20700</v>
+        <v>-16600</v>
       </c>
       <c r="I21" s="3">
-        <v>-13900</v>
+        <v>22300</v>
       </c>
       <c r="J21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-8100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1382,31 +1419,34 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1435,99 +1475,105 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4400</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1535,14 +1581,17 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-39500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>20700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4400</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-39500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>20700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4400</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,41 +1979,44 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-600</v>
+        <v>-1700</v>
       </c>
       <c r="E32" s="3">
-        <v>-5900</v>
+        <v>4300</v>
       </c>
       <c r="F32" s="3">
-        <v>5400</v>
+        <v>8400</v>
       </c>
       <c r="G32" s="3">
-        <v>9500</v>
+        <v>-3500</v>
       </c>
       <c r="H32" s="3">
-        <v>-27600</v>
+        <v>-8600</v>
       </c>
       <c r="I32" s="3">
-        <v>8300</v>
+        <v>29100</v>
       </c>
       <c r="J32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1600</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1965,61 +2035,67 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-39500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>20700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4400</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-39500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>20700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4400</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,69 +2310,73 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E41" s="3">
         <v>8100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2301,11 +2391,11 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>5000</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2321,8 +2411,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2330,38 +2420,41 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
-      </c>
-      <c r="E43" s="3">
-        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
+        <v>200</v>
+      </c>
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2377,14 +2470,17 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2398,23 +2494,23 @@
         <v>2200</v>
       </c>
       <c r="G44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H44" s="3">
         <v>14000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2430,56 +2526,59 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2100</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
-        <v>3300</v>
+        <v>800</v>
       </c>
       <c r="F45" s="3">
-        <v>6100</v>
+        <v>1700</v>
       </c>
       <c r="G45" s="3">
-        <v>6100</v>
+        <v>4200</v>
       </c>
       <c r="H45" s="3">
-        <v>6400</v>
+        <v>1000</v>
       </c>
       <c r="I45" s="3">
-        <v>5700</v>
+        <v>300</v>
       </c>
       <c r="J45" s="3">
+        <v>300</v>
+      </c>
+      <c r="K45" s="3">
         <v>5400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5300</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
       <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,84 +2588,90 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E46" s="3">
         <v>13100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>32100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1400</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
+      <c r="R46" s="3">
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2595,38 +2700,41 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E48" s="3">
         <v>17900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2642,14 +2750,17 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,8 +2924,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2822,7 +2942,7 @@
         <v>200</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -2831,16 +2951,16 @@
         <v>100</v>
       </c>
       <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>174500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>174200</v>
       </c>
       <c r="N52" s="3">
         <v>174200</v>
@@ -2849,19 +2969,22 @@
         <v>174200</v>
       </c>
       <c r="P52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E54" s="3">
         <v>31200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>56300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>48500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>49500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>58000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>174700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>174600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>174800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>175600</v>
-      </c>
-      <c r="P54" s="3">
-        <v>200</v>
       </c>
       <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
+      <c r="R54" s="3">
+        <v>200</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,50 +3138,51 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>5600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>5700</v>
       </c>
       <c r="H57" s="3">
         <v>5700</v>
       </c>
       <c r="I57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
       </c>
       <c r="O57" s="3">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,197 +3192,209 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6100</v>
+        <v>900</v>
       </c>
       <c r="E59" s="3">
-        <v>7300</v>
+        <v>900</v>
       </c>
       <c r="F59" s="3">
-        <v>10400</v>
+        <v>1100</v>
       </c>
       <c r="G59" s="3">
-        <v>7200</v>
+        <v>2800</v>
       </c>
       <c r="H59" s="3">
-        <v>7800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>3600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
-      </c>
-      <c r="N59" s="3">
-        <v>200</v>
       </c>
       <c r="O59" s="3">
         <v>200</v>
       </c>
       <c r="P59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E60" s="3">
         <v>11700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
-      </c>
-      <c r="N60" s="3">
-        <v>300</v>
       </c>
       <c r="O60" s="3">
         <v>300</v>
       </c>
       <c r="P60" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>46600</v>
+        <v>47100</v>
       </c>
       <c r="E61" s="3">
-        <v>44900</v>
+        <v>47700</v>
       </c>
       <c r="F61" s="3">
+        <v>46200</v>
+      </c>
+      <c r="G61" s="3">
+        <v>32200</v>
+      </c>
+      <c r="H61" s="3">
         <v>31600</v>
       </c>
-      <c r="G61" s="3">
-        <v>29900</v>
-      </c>
-      <c r="H61" s="3">
-        <v>17800</v>
-      </c>
       <c r="I61" s="3">
+        <v>18800</v>
+      </c>
+      <c r="J61" s="3">
         <v>16800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3273,50 +3416,53 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2200</v>
+        <v>1300</v>
       </c>
       <c r="E62" s="3">
-        <v>10000</v>
+        <v>1200</v>
       </c>
       <c r="F62" s="3">
-        <v>19000</v>
+        <v>8700</v>
       </c>
       <c r="G62" s="3">
-        <v>16100</v>
+        <v>18400</v>
       </c>
       <c r="H62" s="3">
-        <v>6800</v>
+        <v>14500</v>
       </c>
       <c r="I62" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J62" s="3">
         <v>34900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12700</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E66" s="3">
         <v>60600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>68900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>67900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>59000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>62300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-135100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-123800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-118400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-118800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-79200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-61600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-82200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-68100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-59900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-11600</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
       <c r="Q72" s="3">
         <v>0</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-29400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-39500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-41800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-12800</v>
       </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
       <c r="K76" s="3">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3">
         <v>6300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>167700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>168500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>166500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>162700</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
       <c r="Q76" s="3">
         <v>0</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-39500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>20700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4400</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
         <v>0</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,34 +4419,35 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>100</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -4265,8 +4464,8 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-4100</v>
       </c>
-      <c r="I89" s="3">
-        <v>-8800</v>
-      </c>
       <c r="J89" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-5700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,31 +4833,32 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-4600</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-4600</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,52 +4999,55 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-800</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-4600</v>
       </c>
       <c r="H94" s="3">
         <v>-4600</v>
       </c>
       <c r="I94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J94" s="3">
         <v>3500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -4825,8 +5055,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,31 +5079,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,84 +5301,90 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>10300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12000</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>52900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>800</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>KITT</t>
   </si>
@@ -656,134 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3">
         <v>500</v>
       </c>
       <c r="F8" s="3">
+        <v>400</v>
+      </c>
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
-        <v>1100</v>
-      </c>
       <c r="H8" s="3">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="I8" s="3">
         <v>1100</v>
       </c>
       <c r="J8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L8" s="3">
         <v>2800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5200</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -793,53 +800,59 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F9" s="3">
         <v>2600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>4400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>4400</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,47 +868,53 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F10" s="3">
         <v>-2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-2400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-1600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-3400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -911,8 +930,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,47 +958,49 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>300</v>
       </c>
       <c r="L12" s="3">
         <v>200</v>
       </c>
       <c r="M12" s="3">
+        <v>300</v>
+      </c>
+      <c r="N12" s="3">
+        <v>200</v>
+      </c>
+      <c r="O12" s="3">
         <v>1900</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -989,8 +1016,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1078,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1054,34 +1093,34 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>120100</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>25500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>27300</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1101,47 +1140,53 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
       </c>
       <c r="G15" s="3">
+        <v>400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>400</v>
+      </c>
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
       </c>
       <c r="L15" s="3">
+        <v>300</v>
+      </c>
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
+        <v>100</v>
+      </c>
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1151,14 +1196,20 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,103 +1227,111 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="E17" s="3">
         <v>6500</v>
       </c>
       <c r="F17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H17" s="3">
         <v>6000</v>
       </c>
-      <c r="G17" s="3">
-        <v>13900</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J17" s="3">
         <v>9800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>10400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>9000</v>
       </c>
       <c r="M17" s="3">
         <v>10400</v>
       </c>
       <c r="N17" s="3">
+        <v>9000</v>
+      </c>
+      <c r="O17" s="3">
+        <v>10400</v>
+      </c>
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5600</v>
+        <v>-5900</v>
       </c>
       <c r="E18" s="3">
         <v>-6000</v>
       </c>
       <c r="F18" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-12900</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-8200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-7200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-6000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5200</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,8 +1347,14 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,47 +1375,49 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-8400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>8600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-29100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-7100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1366,47 +1433,53 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-6800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="J21" s="3">
         <v>-16600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>22300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-8900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-8100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-12800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-6900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1422,38 +1495,44 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F22" s="3">
         <v>4100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>3700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>2500</v>
       </c>
-      <c r="G22" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>4900</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1478,64 +1557,76 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-118600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-11400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-39500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-17700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>20700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-14100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-13200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1560,8 +1651,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1572,26 +1663,32 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1743,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-118600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-11400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-39500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-17700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>20700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-14100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-13200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-118600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-11400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-39500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-17700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>20700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-14100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-18100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,47 +2115,53 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>8400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-8600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>29100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>7100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2038,64 +2177,76 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-118600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-11400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-39500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-17700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>20700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-14100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-18100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2301,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-118600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-11400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-39500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-17700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>20700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-14100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-18100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2482,72 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F41" s="3">
         <v>2900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>17800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>35900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2394,14 +2573,14 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>5000</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2414,53 +2593,59 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,22 +2658,28 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="E44" s="3">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="F44" s="3">
         <v>2200</v>
@@ -2497,26 +2688,26 @@
         <v>2200</v>
       </c>
       <c r="H44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J44" s="3">
         <v>14000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>12500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>11000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5600</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2529,14 +2720,20 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2544,111 +2741,123 @@
         <v>700</v>
       </c>
       <c r="E45" s="3">
+        <v>600</v>
+      </c>
+      <c r="F45" s="3">
+        <v>700</v>
+      </c>
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5300</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F46" s="3">
         <v>7300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>13100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>27900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>25200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>32100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>37000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>48000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2673,11 +2882,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2703,44 +2912,50 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17400</v>
+        <v>23800</v>
       </c>
       <c r="E48" s="3">
-        <v>17900</v>
+        <v>18200</v>
       </c>
       <c r="F48" s="3">
         <v>17400</v>
       </c>
       <c r="G48" s="3">
+        <v>17900</v>
+      </c>
+      <c r="H48" s="3">
+        <v>17400</v>
+      </c>
+      <c r="I48" s="3">
         <v>16700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>28400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>23200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>17200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>15500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>10000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2753,19 +2968,25 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -2815,8 +3036,14 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3160,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2945,46 +3184,52 @@
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
       <c r="M52" s="3">
+        <v>200</v>
+      </c>
+      <c r="N52" s="3">
+        <v>100</v>
+      </c>
+      <c r="O52" s="3">
         <v>174500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>174200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>174200</v>
       </c>
       <c r="P52" s="3">
         <v>174200</v>
       </c>
       <c r="Q52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="R52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3284,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F54" s="3">
         <v>25000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>31200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>26100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>56300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>48500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>49500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>52600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>58000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>174700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>174600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>174800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>175600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,69 +3398,77 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2800</v>
       </c>
       <c r="M57" s="3">
         <v>300</v>
       </c>
       <c r="N57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O57" s="3">
+        <v>300</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>2900</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
@@ -3210,197 +3477,215 @@
         <v>400</v>
       </c>
       <c r="G58" s="3">
+        <v>400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>3600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F60" s="3">
         <v>13100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>11700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>14000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>17400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>13000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>13600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>10600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F61" s="3">
         <v>47100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>47700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>46200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>32200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>31600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>18800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>16800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>15900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>15000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3419,64 +3704,76 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>8700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>18400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>14500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>34900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>32800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>32400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>8000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>12700</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3952,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>43100</v>
+      </c>
+      <c r="F66" s="3">
         <v>61500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>60600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>68900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>67900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>59000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>38200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>62300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>52600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>51800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>8300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +4162,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4286,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-261300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-253700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-135100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-123800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-118400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-118800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-79200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-61600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-82200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-68100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-59900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-6700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-5800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-7700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3">
+        <v>0</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4534,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-36500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-29400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-39500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-41800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-2700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-12800</v>
       </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3">
         <v>6300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>167700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>168500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>166500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>162700</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S76" s="3">
+        <v>0</v>
+      </c>
+      <c r="T76" s="3">
+        <v>0</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4658,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-118600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-11400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-39500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-17700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>20700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-14100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-18100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,25 +4815,27 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -4449,11 +4846,11 @@
       <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
+        <v>100</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -4467,17 +4864,23 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +5183,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-8400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-6700</v>
       </c>
-      <c r="G89" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="J89" s="3">
         <v>-3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-8900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-30800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,38 +5273,40 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-4600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -4890,8 +5331,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5455,76 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>3500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-12400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5545,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5106,11 +5573,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5136,8 +5603,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5789,76 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="E100" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>10300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>12000</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
         <v>10700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>52900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5386,11 +5883,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5416,60 +5913,72 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-8100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-18100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>15300</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-200</v>
       </c>
       <c r="O102" s="3">
         <v>-300</v>
       </c>
       <c r="P102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>KITT</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>500</v>
       </c>
       <c r="H8" s="3">
         <v>500</v>
       </c>
       <c r="I8" s="3">
+        <v>500</v>
+      </c>
+      <c r="J8" s="3">
         <v>1100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5200</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -806,56 +810,59 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4400</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -874,50 +881,53 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-2300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-2400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-3400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,50 +973,51 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,46 +1101,49 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>120100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>78700</v>
+      </c>
+      <c r="J14" s="3">
         <v>27300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1146,19 +1166,22 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
         <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
         <v>400</v>
@@ -1167,29 +1190,29 @@
         <v>400</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
       </c>
       <c r="K15" s="3">
+        <v>200</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>300</v>
-      </c>
-      <c r="M15" s="3">
-        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
       </c>
       <c r="O15" s="3">
+        <v>100</v>
+      </c>
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1202,14 +1225,17 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,112 +1255,116 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E17" s="3">
         <v>6000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1353,8 +1383,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,50 +1410,51 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4300</v>
-      </c>
       <c r="H20" s="3">
-        <v>-8400</v>
+        <v>-11700</v>
       </c>
       <c r="I20" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="J20" s="3">
         <v>3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-29100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1600</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,50 +1473,53 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1300</v>
-      </c>
       <c r="H21" s="3">
-        <v>3300</v>
+        <v>6100</v>
       </c>
       <c r="I21" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J21" s="3">
         <v>-10600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>22300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1501,41 +1538,44 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-9100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="G22" s="3">
-        <v>3700</v>
-      </c>
       <c r="H22" s="3">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="I22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4900</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1563,70 +1603,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-118600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11400</v>
       </c>
-      <c r="G23" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H23" s="3">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="I23" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-39500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4400</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1657,23 +1703,23 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1681,14 +1727,17 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-118600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H26" s="3">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="I26" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="J26" s="3">
         <v>-39500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4400</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-118600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H27" s="3">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="I27" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="J27" s="3">
         <v>-39500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4400</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,50 +2188,53 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
-        <v>4300</v>
-      </c>
       <c r="H32" s="3">
-        <v>8400</v>
+        <v>11700</v>
       </c>
       <c r="I32" s="3">
+        <v>12900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>29100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1600</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,70 +2253,76 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-118600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H33" s="3">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="I33" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="J33" s="3">
         <v>-39500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>20700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4400</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-118600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H35" s="3">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="I35" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="J35" s="3">
         <v>-39500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>20700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4400</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E41" s="3">
         <v>10100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>35900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>800</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2579,11 +2669,11 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>5000</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2599,8 +2689,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2608,47 +2698,50 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
-      </c>
-      <c r="H43" s="3">
-        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2664,25 +2757,28 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>900</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2200</v>
       </c>
       <c r="G44" s="3">
         <v>2200</v>
@@ -2694,23 +2790,23 @@
         <v>2200</v>
       </c>
       <c r="J44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K44" s="3">
         <v>14000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5600</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,14 +2822,17 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2741,50 +2840,50 @@
         <v>700</v>
       </c>
       <c r="E45" s="3">
+        <v>700</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>300</v>
       </c>
       <c r="M45" s="3">
+        <v>300</v>
+      </c>
+      <c r="N45" s="3">
         <v>5400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5300</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
       <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,70 +2893,76 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>32100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>48000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1400</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
       <c r="T46" s="3">
         <v>0</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
+      <c r="U46" s="3">
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2888,8 +2993,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2918,47 +3023,50 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E48" s="3">
         <v>23800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2974,14 +3082,17 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2989,7 +3100,7 @@
         <v>10700</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,13 +3283,16 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
@@ -3190,7 +3310,7 @@
         <v>200</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -3199,16 +3319,16 @@
         <v>100</v>
       </c>
       <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>174500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>174200</v>
       </c>
       <c r="Q52" s="3">
         <v>174200</v>
@@ -3217,19 +3337,22 @@
         <v>174200</v>
       </c>
       <c r="S52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E54" s="3">
         <v>48500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>48500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>49500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>52600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>174700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>174600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>174800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>175600</v>
-      </c>
-      <c r="S54" s="3">
-        <v>200</v>
       </c>
       <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
+      <c r="U54" s="3">
+        <v>200</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,59 +3530,60 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>5700</v>
       </c>
       <c r="K57" s="3">
         <v>5700</v>
       </c>
       <c r="L57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
       </c>
       <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3462,8 +3593,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3471,7 +3605,7 @@
         <v>2900</v>
       </c>
       <c r="E58" s="3">
-        <v>400</v>
+        <v>2900</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
@@ -3483,49 +3617,52 @@
         <v>400</v>
       </c>
       <c r="I58" s="3">
+        <v>400</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3536,159 +3673,165 @@
         <v>300</v>
       </c>
       <c r="F59" s="3">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="G59" s="3">
         <v>900</v>
       </c>
       <c r="H59" s="3">
+        <v>900</v>
+      </c>
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>3600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>100</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>200</v>
       </c>
       <c r="R59" s="3">
         <v>200</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E60" s="3">
         <v>17800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11700</v>
       </c>
-      <c r="H60" s="3">
-        <v>14000</v>
-      </c>
       <c r="I60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J60" s="3">
         <v>17400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>300</v>
       </c>
       <c r="R60" s="3">
         <v>300</v>
       </c>
       <c r="S60" s="3">
+        <v>300</v>
+      </c>
+      <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E61" s="3">
         <v>28100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47700</v>
       </c>
-      <c r="H61" s="3">
-        <v>46200</v>
-      </c>
       <c r="I61" s="3">
+        <v>119800</v>
+      </c>
+      <c r="J61" s="3">
         <v>32200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3710,8 +3853,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3719,50 +3865,50 @@
         <v>1000</v>
       </c>
       <c r="E62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>32400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12700</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E66" s="3">
         <v>47000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>61500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60600</v>
       </c>
-      <c r="H66" s="3">
-        <v>68900</v>
-      </c>
       <c r="I66" s="3">
+        <v>142200</v>
+      </c>
+      <c r="J66" s="3">
         <v>67900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-268700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-261300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-253700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-135100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-123800</v>
       </c>
-      <c r="H72" s="3">
-        <v>-118400</v>
-      </c>
       <c r="I72" s="3">
+        <v>-191600</v>
+      </c>
+      <c r="J72" s="3">
         <v>-118800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-61600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-82200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-68100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-59900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11600</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-20400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-36500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-29400</v>
       </c>
-      <c r="H76" s="3">
-        <v>-39500</v>
-      </c>
       <c r="I76" s="3">
+        <v>-112800</v>
+      </c>
+      <c r="J76" s="3">
         <v>-41800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-2700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-12800</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
       <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
         <v>6300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>167700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>168500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>166500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>162700</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
       <c r="T76" s="3">
         <v>0</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-118600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H81" s="3">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="I81" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="J81" s="3">
         <v>-39500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>20700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4400</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4826,19 +5025,19 @@
         <v>400</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
+        <v>200</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -4852,8 +5051,8 @@
       <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>100</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -4870,8 +5069,8 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5287,29 +5508,29 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-4600</v>
       </c>
       <c r="K91" s="3">
         <v>-4600</v>
       </c>
       <c r="L91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,61 +5688,64 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-4600</v>
       </c>
       <c r="K94" s="3">
         <v>-4600</v>
       </c>
       <c r="L94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="M94" s="3">
         <v>3500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12400</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5579,8 +5813,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>19400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>10300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>52900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5889,8 +6138,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>8900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
@@ -3887,7 +3887,7 @@
         <v>13100</v>
       </c>
       <c r="I60" s="3">
-        <v>11700</v>
+        <v>10900</v>
       </c>
       <c r="J60" s="3">
         <v>13700</v>
@@ -3955,7 +3955,7 @@
         <v>47100</v>
       </c>
       <c r="I61" s="3">
-        <v>47700</v>
+        <v>110500</v>
       </c>
       <c r="J61" s="3">
         <v>119800</v>
@@ -4295,7 +4295,7 @@
         <v>61500</v>
       </c>
       <c r="I66" s="3">
-        <v>60600</v>
+        <v>122600</v>
       </c>
       <c r="J66" s="3">
         <v>142200</v>
@@ -4661,7 +4661,7 @@
         <v>-135100</v>
       </c>
       <c r="I72" s="3">
-        <v>-123800</v>
+        <v>-187100</v>
       </c>
       <c r="J72" s="3">
         <v>-191600</v>
@@ -4933,7 +4933,7 @@
         <v>-36500</v>
       </c>
       <c r="I76" s="3">
-        <v>-29400</v>
+        <v>-91500</v>
       </c>
       <c r="J76" s="3">
         <v>-112800</v>

--- a/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KITT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>KITT</t>
   </si>
@@ -656,161 +656,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F8" s="3">
         <v>2000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>500</v>
-      </c>
-      <c r="H8" s="3">
-        <v>400</v>
       </c>
       <c r="I8" s="3">
         <v>500</v>
       </c>
       <c r="J8" s="3">
+        <v>400</v>
+      </c>
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
-        <v>1100</v>
-      </c>
       <c r="L8" s="3">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="M8" s="3">
         <v>1100</v>
       </c>
       <c r="N8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P8" s="3">
         <v>2800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>5200</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,65 +827,71 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F9" s="3">
         <v>4300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>4400</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -894,59 +907,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G10" s="3">
         <v>-1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-1100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-2400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-1600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-3400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,8 +981,14 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1013,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1002,45 +1029,45 @@
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="3">
-        <v>0</v>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
-      </c>
-      <c r="N12" s="3">
-        <v>200</v>
-      </c>
-      <c r="O12" s="3">
-        <v>300</v>
       </c>
       <c r="P12" s="3">
         <v>200</v>
       </c>
       <c r="Q12" s="3">
+        <v>300</v>
+      </c>
+      <c r="R12" s="3">
+        <v>200</v>
+      </c>
+      <c r="S12" s="3">
         <v>1900</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1056,8 +1083,14 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,55 +1157,61 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>8600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>120100</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>77500</v>
+      </c>
+      <c r="J14" s="3">
         <v>-24200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>78700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>27300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1192,8 +1231,14 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1201,50 +1246,50 @@
         <v>600</v>
       </c>
       <c r="E15" s="3">
+        <v>700</v>
+      </c>
+      <c r="F15" s="3">
         <v>600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
+        <v>600</v>
+      </c>
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>400</v>
       </c>
       <c r="J15" s="3">
         <v>400</v>
       </c>
       <c r="K15" s="3">
+        <v>400</v>
+      </c>
+      <c r="L15" s="3">
+        <v>400</v>
+      </c>
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>200</v>
-      </c>
-      <c r="M15" s="3">
-        <v>100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>300</v>
       </c>
       <c r="O15" s="3">
         <v>100</v>
       </c>
       <c r="P15" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q15" s="3">
         <v>100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
+        <v>100</v>
+      </c>
+      <c r="S15" s="3">
         <v>200</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,14 +1299,20 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,127 +1334,135 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F17" s="3">
         <v>7900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
+        <v>6100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="G17" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>5900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>6000</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>9800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>8000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>8600</v>
-      </c>
-      <c r="O17" s="3">
-        <v>10400</v>
-      </c>
-      <c r="P17" s="3">
-        <v>9000</v>
       </c>
       <c r="Q17" s="3">
         <v>10400</v>
       </c>
       <c r="R17" s="3">
+        <v>9000</v>
+      </c>
+      <c r="S17" s="3">
+        <v>10400</v>
+      </c>
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5900</v>
+        <v>-5700</v>
       </c>
       <c r="E18" s="3">
-        <v>-6400</v>
+        <v>-5600</v>
       </c>
       <c r="F18" s="3">
         <v>-5900</v>
       </c>
       <c r="G18" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-6000</v>
       </c>
-      <c r="H18" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="R18" s="3">
         <v>-6000</v>
       </c>
-      <c r="J18" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,8 +1478,14 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,59 +1510,61 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1600</v>
-      </c>
       <c r="H20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-11700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-12900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>8600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-29100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-1600</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1513,59 +1580,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-5700</v>
       </c>
-      <c r="F21" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-7200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J21" s="3">
         <v>-4700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>6100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>7800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-10600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-16600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>22300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-8900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-8100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-6900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,50 +1654,56 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="G22" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>1600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>4900</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1649,76 +1728,88 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-7500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-7600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-118600</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="J23" s="3">
         <v>17900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-72800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-39500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-17700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>20700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-14100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-8200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4400</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1755,8 +1846,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1767,26 +1858,32 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1950,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-7500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-7600</v>
       </c>
-      <c r="G26" s="3">
-        <v>-118600</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="J26" s="3">
         <v>17900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-72800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-39500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-17700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>20700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-14100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-8200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-6900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4400</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-44700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-10100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-7500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-7600</v>
       </c>
-      <c r="G27" s="3">
-        <v>-118600</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="J27" s="3">
         <v>17900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-72800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-39500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-17700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>20700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-14100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-8200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-6900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4400</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2172,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2246,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2320,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,59 +2394,65 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>300</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H32" s="3">
+        <v>200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>11700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>12900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-8600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>29100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>7100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>1600</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,76 +2468,88 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-7500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-7600</v>
       </c>
-      <c r="G33" s="3">
-        <v>-118600</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="J33" s="3">
         <v>17900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-72800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-39500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-17700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>20700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-14100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-8200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-6900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4400</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2616,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-7500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-7600</v>
       </c>
-      <c r="G35" s="3">
-        <v>-118600</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="J35" s="3">
         <v>17900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-72800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-39500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-17700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>20700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-14100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-8200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-6900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4400</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2801,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2829,84 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F41" s="3">
         <v>5500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>17800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>35900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2765,14 +2944,14 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>5000</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2785,65 +2964,71 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,34 +3041,40 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>900</v>
-      </c>
-      <c r="E44" s="3">
-        <v>900</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1000</v>
       </c>
       <c r="G44" s="3">
         <v>900</v>
       </c>
       <c r="H44" s="3">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="I44" s="3">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="J44" s="3">
         <v>2200</v>
@@ -2892,26 +3083,26 @@
         <v>2200</v>
       </c>
       <c r="L44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N44" s="3">
         <v>14000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>12500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>11000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,150 +3115,168 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>600</v>
       </c>
       <c r="H45" s="3">
         <v>700</v>
       </c>
       <c r="I45" s="3">
+        <v>600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>700</v>
+      </c>
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>5300</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F46" s="3">
         <v>9600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>13100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>11800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>9200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>27900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>25200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>32100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>37000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>48000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1400</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3104,11 +3313,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3134,56 +3343,62 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E48" s="3">
         <v>22400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>22400</v>
+      </c>
+      <c r="G48" s="3">
         <v>23100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>23800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>18200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>17400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>17900</v>
       </c>
       <c r="J48" s="3">
         <v>17400</v>
       </c>
       <c r="K48" s="3">
+        <v>17900</v>
+      </c>
+      <c r="L48" s="3">
+        <v>17400</v>
+      </c>
+      <c r="M48" s="3">
         <v>16700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>28400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>23200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>17200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>15500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>10000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,31 +3411,37 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="E49" s="3">
-        <v>10700</v>
+        <v>10900</v>
       </c>
       <c r="F49" s="3">
         <v>10700</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -3270,8 +3491,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3565,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3639,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3418,10 +3657,10 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
@@ -3436,46 +3675,52 @@
         <v>200</v>
       </c>
       <c r="L52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
       </c>
       <c r="Q52" s="3">
+        <v>200</v>
+      </c>
+      <c r="R52" s="3">
+        <v>100</v>
+      </c>
+      <c r="S52" s="3">
         <v>174500</v>
-      </c>
-      <c r="R52" s="3">
-        <v>174200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>174200</v>
       </c>
       <c r="T52" s="3">
         <v>174200</v>
       </c>
       <c r="U52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="V52" s="3">
+        <v>174200</v>
+      </c>
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3787,88 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>42600</v>
+      </c>
+      <c r="F54" s="3">
         <v>42800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>41900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>48500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>22700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>25000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>31200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>26100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>56300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>48500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>49500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>52600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>58000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>174700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>174600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>174800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>175600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3893,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,93 +3921,101 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F57" s="3">
         <v>4400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>5900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>2800</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
       </c>
       <c r="R57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S57" s="3">
+        <v>300</v>
+      </c>
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F58" s="3">
         <v>30500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2900</v>
-      </c>
-      <c r="G58" s="3">
-        <v>400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>400</v>
       </c>
       <c r="I58" s="3">
         <v>400</v>
@@ -3757,233 +4024,251 @@
         <v>400</v>
       </c>
       <c r="K58" s="3">
+        <v>400</v>
+      </c>
+      <c r="L58" s="3">
+        <v>400</v>
+      </c>
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>4000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>300</v>
       </c>
       <c r="G59" s="3">
         <v>300</v>
       </c>
       <c r="H59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>3600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>35400</v>
+      </c>
+      <c r="F60" s="3">
         <v>46500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>18300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>17800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>12300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>13100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>13700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>17400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>13000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>10600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>28200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>28100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>29700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>47100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>110500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>119800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>32200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>31600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>18800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>16800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>15900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>15000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4002,76 +4287,88 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>8700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>18400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>14500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>34900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>32800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>32400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>5100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>5600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>8000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>12700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4435,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4509,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4583,88 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>35600</v>
+      </c>
+      <c r="F66" s="3">
         <v>46900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>47600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>47000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>43100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>61500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>122600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>142200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>67900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>59000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>38200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>62300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>52600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>51800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>7000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>6100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>8300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>12900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4689,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4759,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4833,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4907,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4981,88 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-333000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-323500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-278800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-268700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-261300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-253700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-135100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-187100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-191600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-118800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-79200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-61600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-82200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-68100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-59900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-6700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-5800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-7700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-11600</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +5129,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5203,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5277,88 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F76" s="3">
         <v>-4100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-5700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-20400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-36500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-91500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-112800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-41800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-2700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>10300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-12800</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
+        <v>0</v>
+      </c>
+      <c r="R76" s="3">
         <v>6300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>167700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>168500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>166500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>162700</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5425,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-7500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-7600</v>
       </c>
-      <c r="G81" s="3">
-        <v>-118600</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="J81" s="3">
         <v>17900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-72800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-39500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-17700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>20700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-14100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-8200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-6900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4400</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,37 +5610,39 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
       </c>
       <c r="G83" s="3">
+        <v>400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -5256,11 +5653,11 @@
       <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>100</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -5274,17 +5671,23 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5754,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5828,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5902,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5976,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +6050,88 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-6600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="O89" s="3">
         <v>-4100</v>
       </c>
-      <c r="H89" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-8900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-5700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-30800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,16 +6156,18 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -5735,32 +6176,32 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-4600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -5785,8 +6226,14 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6300,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6374,88 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-3900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-4600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>3500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-12400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6480,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6053,11 +6520,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6083,8 +6550,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6624,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6698,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,87 +6772,99 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F100" s="3">
         <v>7800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>19400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>10300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>12000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>10700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>52900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -6393,11 +6890,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6423,72 +6920,84 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F102" s="3">
         <v>2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>8900</v>
       </c>
-      <c r="G102" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-6000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-18100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>15300</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-200</v>
       </c>
       <c r="S102" s="3">
         <v>-300</v>
       </c>
       <c r="T102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3" t="s">
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
